--- a/output/Tables/Best practice/HIA_area_2019_1000replicate.xlsx
+++ b/output/Tables/Best practice/HIA_area_2019_1000replicate.xlsx
@@ -438,22 +438,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>18709.884</v>
+        <v>18709.518</v>
       </c>
       <c r="D2">
-        <v>15811.961</v>
+        <v>15811.065</v>
       </c>
       <c r="E2">
-        <v>21609.973</v>
+        <v>21609.165</v>
       </c>
       <c r="F2">
-        <v>161561.55</v>
+        <v>161536.56</v>
       </c>
       <c r="G2">
-        <v>145637.899</v>
+        <v>145628.173</v>
       </c>
       <c r="H2">
-        <v>177508.411</v>
+        <v>177507.287</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>21488634772.398</v>
+        <v>21485999730.23</v>
       </c>
       <c r="M2">
-        <v>19360625330.183</v>
+        <v>19358985171.655</v>
       </c>
       <c r="N2">
-        <v>23609912521.618</v>
+        <v>23606061479.792</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>12851.667</v>
+        <v>12848.69</v>
       </c>
       <c r="D3">
-        <v>10839.544</v>
+        <v>10835.714</v>
       </c>
       <c r="E3">
-        <v>14859.037</v>
+        <v>14854.298</v>
       </c>
       <c r="F3">
-        <v>118829.1</v>
+        <v>118815.277</v>
       </c>
       <c r="G3">
-        <v>106325.357</v>
+        <v>106310.472</v>
       </c>
       <c r="H3">
-        <v>131333.31</v>
+        <v>131321.229</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>15802222012.321</v>
+        <v>15800204998.341</v>
       </c>
       <c r="M3">
-        <v>14132564101.027</v>
+        <v>14133153075.181</v>
       </c>
       <c r="N3">
-        <v>17481116859.602</v>
+        <v>17479978231.69</v>
       </c>
     </row>
     <row r="4">
@@ -534,22 +534,22 @@
         </is>
       </c>
       <c r="C4">
-        <v>30171.125</v>
+        <v>30171.162</v>
       </c>
       <c r="D4">
-        <v>26872.95</v>
+        <v>26869.348</v>
       </c>
       <c r="E4">
-        <v>33458.428</v>
+        <v>33453.654</v>
       </c>
       <c r="F4">
-        <v>301902.977</v>
+        <v>301859.196</v>
       </c>
       <c r="G4">
-        <v>281818.816</v>
+        <v>281834.368</v>
       </c>
       <c r="H4">
-        <v>321995.17</v>
+        <v>321920.685</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -561,13 +561,13 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>40163335783.855</v>
+        <v>40158212097.038</v>
       </c>
       <c r="M4">
-        <v>37484548614.31</v>
+        <v>37478846588.796</v>
       </c>
       <c r="N4">
-        <v>42851436660.3</v>
+        <v>42847726345.743</v>
       </c>
     </row>
     <row r="5">
@@ -582,40 +582,40 @@
         </is>
       </c>
       <c r="C5">
-        <v>10794.756</v>
+        <v>10802.058</v>
       </c>
       <c r="D5">
-        <v>9413.177</v>
+        <v>9421.721</v>
       </c>
       <c r="E5">
-        <v>12187.864</v>
+        <v>12202.713</v>
       </c>
       <c r="F5">
-        <v>8768.531000000001</v>
+        <v>8773.638000000001</v>
       </c>
       <c r="G5">
-        <v>7751.298</v>
+        <v>7754.614</v>
       </c>
       <c r="H5">
-        <v>9796.137000000001</v>
+        <v>9804.384</v>
       </c>
       <c r="I5">
-        <v>601236855.984</v>
+        <v>601799885.202</v>
       </c>
       <c r="J5">
-        <v>524331956.664</v>
+        <v>524456934.694</v>
       </c>
       <c r="K5">
-        <v>678880740.229</v>
+        <v>679679086.267</v>
       </c>
       <c r="L5">
-        <v>1166151988.079</v>
+        <v>1166868997.226</v>
       </c>
       <c r="M5">
-        <v>1030794434.683</v>
+        <v>1031341411.92</v>
       </c>
       <c r="N5">
-        <v>1303166543.628</v>
+        <v>1303984640.817</v>
       </c>
     </row>
     <row r="6">
@@ -630,40 +630,40 @@
         </is>
       </c>
       <c r="C6">
-        <v>7942.721</v>
+        <v>7949.328</v>
       </c>
       <c r="D6">
-        <v>6860.745</v>
+        <v>6865.482</v>
       </c>
       <c r="E6">
-        <v>9043.062</v>
+        <v>9047.485000000001</v>
       </c>
       <c r="F6">
-        <v>6657.978</v>
+        <v>6664.169</v>
       </c>
       <c r="G6">
-        <v>5813.769</v>
+        <v>5818.051</v>
       </c>
       <c r="H6">
-        <v>7510.866</v>
+        <v>7518.382</v>
       </c>
       <c r="I6">
-        <v>442612228.602</v>
+        <v>443050678.994</v>
       </c>
       <c r="J6">
-        <v>382142454.358</v>
+        <v>382320354.342</v>
       </c>
       <c r="K6">
-        <v>503812293.288</v>
+        <v>504286726.525</v>
       </c>
       <c r="L6">
-        <v>885845578.373</v>
+        <v>886595455.7819999</v>
       </c>
       <c r="M6">
-        <v>773534034.557</v>
+        <v>774428953.976</v>
       </c>
       <c r="N6">
-        <v>999076563.545</v>
+        <v>1000087810.552</v>
       </c>
     </row>
     <row r="7">
@@ -678,40 +678,40 @@
         </is>
       </c>
       <c r="C7">
-        <v>17345.313</v>
+        <v>17364.909</v>
       </c>
       <c r="D7">
-        <v>15759.308</v>
+        <v>15768.036</v>
       </c>
       <c r="E7">
-        <v>18944.975</v>
+        <v>18968.923</v>
       </c>
       <c r="F7">
-        <v>15149.258</v>
+        <v>15170.243</v>
       </c>
       <c r="G7">
-        <v>13952.621</v>
+        <v>13968.943</v>
       </c>
       <c r="H7">
-        <v>16353.802</v>
+        <v>16379.719</v>
       </c>
       <c r="I7">
-        <v>966477558.715</v>
+        <v>967536669.8099999</v>
       </c>
       <c r="J7">
-        <v>877448563.069</v>
+        <v>878124212.0549999</v>
       </c>
       <c r="K7">
-        <v>1055991104.497</v>
+        <v>1057117158.918</v>
       </c>
       <c r="L7">
-        <v>2014876848.883</v>
+        <v>2017783520.204</v>
       </c>
       <c r="M7">
-        <v>1856234784.92</v>
+        <v>1858176666.824</v>
       </c>
       <c r="N7">
-        <v>2174751138.94</v>
+        <v>2178591713.352</v>
       </c>
     </row>
     <row r="8">
@@ -726,40 +726,40 @@
         </is>
       </c>
       <c r="C8">
-        <v>6322.387</v>
+        <v>6328.284</v>
       </c>
       <c r="D8">
-        <v>5596.287</v>
+        <v>5601.263</v>
       </c>
       <c r="E8">
-        <v>7071.273</v>
+        <v>7082.131</v>
       </c>
       <c r="F8">
-        <v>8352.916999999999</v>
+        <v>8375.709000000001</v>
       </c>
       <c r="G8">
-        <v>7173.39</v>
+        <v>7187.591</v>
       </c>
       <c r="H8">
-        <v>9609.014999999999</v>
+        <v>9648.691000000001</v>
       </c>
       <c r="I8">
-        <v>93601734.757</v>
+        <v>93674898.602</v>
       </c>
       <c r="J8">
-        <v>82886201.104</v>
+        <v>82971631.161</v>
       </c>
       <c r="K8">
-        <v>104639308.022</v>
+        <v>104795432.599</v>
       </c>
       <c r="L8">
-        <v>1110760921.017</v>
+        <v>1113843535.42</v>
       </c>
       <c r="M8">
-        <v>953841831.9170001</v>
+        <v>955539104.852</v>
       </c>
       <c r="N8">
-        <v>1278123357.743</v>
+        <v>1283663404.528</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>5024.216</v>
+        <v>5023.372</v>
       </c>
       <c r="D9">
-        <v>4368.345</v>
+        <v>4374.372</v>
       </c>
       <c r="E9">
-        <v>5699.72</v>
+        <v>5701.688</v>
       </c>
       <c r="F9">
-        <v>6874.198</v>
+        <v>6880.687</v>
       </c>
       <c r="G9">
-        <v>5790.63</v>
+        <v>5798.369</v>
       </c>
       <c r="H9">
-        <v>8015.939</v>
+        <v>8027.495</v>
       </c>
       <c r="I9">
-        <v>74356648.912</v>
+        <v>74362229.212</v>
       </c>
       <c r="J9">
-        <v>64744684.806</v>
+        <v>64801949.128</v>
       </c>
       <c r="K9">
-        <v>84428190.228</v>
+        <v>84397894.25300001</v>
       </c>
       <c r="L9">
-        <v>914167249.459</v>
+        <v>914899168.492</v>
       </c>
       <c r="M9">
-        <v>769594380.017</v>
+        <v>769798371.097</v>
       </c>
       <c r="N9">
-        <v>1066082769.577</v>
+        <v>1067890887.04</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>11476.817</v>
+        <v>11480.408</v>
       </c>
       <c r="D10">
-        <v>10533.946</v>
+        <v>10541.672</v>
       </c>
       <c r="E10">
-        <v>12451.521</v>
+        <v>12448.786</v>
       </c>
       <c r="F10">
-        <v>17280.257</v>
+        <v>17306.57</v>
       </c>
       <c r="G10">
-        <v>15679.82</v>
+        <v>15704.659</v>
       </c>
       <c r="H10">
-        <v>18922.408</v>
+        <v>18964.28</v>
       </c>
       <c r="I10">
-        <v>169940220.281</v>
+        <v>169980171.807</v>
       </c>
       <c r="J10">
-        <v>156023771.45</v>
+        <v>156128766.403</v>
       </c>
       <c r="K10">
-        <v>184444437.724</v>
+        <v>184396841.047</v>
       </c>
       <c r="L10">
-        <v>2297824221.797</v>
+        <v>2301266295.647</v>
       </c>
       <c r="M10">
-        <v>2086474829.615</v>
+        <v>2089304566.671</v>
       </c>
       <c r="N10">
-        <v>2516936357.828</v>
+        <v>2520471538.772</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>1269.522</v>
+        <v>1269.641</v>
       </c>
       <c r="D11">
-        <v>1107.8</v>
+        <v>1108.394</v>
       </c>
       <c r="E11">
-        <v>1438.027</v>
+        <v>1436.858</v>
       </c>
       <c r="F11">
-        <v>2182.65</v>
+        <v>2179.62</v>
       </c>
       <c r="G11">
-        <v>1895.952</v>
+        <v>1895.781</v>
       </c>
       <c r="H11">
-        <v>2484.84</v>
+        <v>2480.778</v>
       </c>
       <c r="I11">
-        <v>95482288.48199999</v>
+        <v>95494883.751</v>
       </c>
       <c r="J11">
-        <v>83301889.55500001</v>
+        <v>83375998.47</v>
       </c>
       <c r="K11">
-        <v>108135010.005</v>
+        <v>108061055.12</v>
       </c>
       <c r="L11">
-        <v>290295102.456</v>
+        <v>289941405.768</v>
       </c>
       <c r="M11">
-        <v>251918675.212</v>
+        <v>251890504.908</v>
       </c>
       <c r="N11">
-        <v>330311324.666</v>
+        <v>329874127.609</v>
       </c>
     </row>
     <row r="12">
@@ -918,40 +918,40 @@
         </is>
       </c>
       <c r="C12">
-        <v>1009.265</v>
+        <v>1011.097</v>
       </c>
       <c r="D12">
-        <v>863.78</v>
+        <v>865.388</v>
       </c>
       <c r="E12">
-        <v>1160.85</v>
+        <v>1161.368</v>
       </c>
       <c r="F12">
-        <v>1837.143</v>
+        <v>1839.56</v>
       </c>
       <c r="G12">
-        <v>1560.583</v>
+        <v>1561.501</v>
       </c>
       <c r="H12">
-        <v>2127.285</v>
+        <v>2128.778</v>
       </c>
       <c r="I12">
-        <v>75924720.087</v>
+        <v>76039824.15000001</v>
       </c>
       <c r="J12">
-        <v>65042107.974</v>
+        <v>65132952.488</v>
       </c>
       <c r="K12">
-        <v>87347693.022</v>
+        <v>87416410.662</v>
       </c>
       <c r="L12">
-        <v>244336426.267</v>
+        <v>244679252.785</v>
       </c>
       <c r="M12">
-        <v>207574451.623</v>
+        <v>207790990.684</v>
       </c>
       <c r="N12">
-        <v>283012182.246</v>
+        <v>282991487.343</v>
       </c>
     </row>
     <row r="13">
@@ -966,40 +966,40 @@
         </is>
       </c>
       <c r="C13">
-        <v>2274.68</v>
+        <v>2277.067</v>
       </c>
       <c r="D13">
-        <v>2076.716</v>
+        <v>2078.428</v>
       </c>
       <c r="E13">
-        <v>2477.904</v>
+        <v>2480.237</v>
       </c>
       <c r="F13">
-        <v>4457.809</v>
+        <v>4455.515</v>
       </c>
       <c r="G13">
-        <v>4071.096</v>
+        <v>4069.207</v>
       </c>
       <c r="H13">
-        <v>4857.738</v>
+        <v>4854.111</v>
       </c>
       <c r="I13">
-        <v>171079953.13</v>
+        <v>171253029.415</v>
       </c>
       <c r="J13">
-        <v>156201100.044</v>
+        <v>156330289.972</v>
       </c>
       <c r="K13">
-        <v>186369766.343</v>
+        <v>186558295.774</v>
       </c>
       <c r="L13">
-        <v>592850137.059</v>
+        <v>592554916.035</v>
       </c>
       <c r="M13">
-        <v>541443402.592</v>
+        <v>541185663.191</v>
       </c>
       <c r="N13">
-        <v>645844025.627</v>
+        <v>645285204.867</v>
       </c>
     </row>
     <row r="14">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="C14">
-        <v>3852.778</v>
+        <v>3853.328</v>
       </c>
       <c r="D14">
-        <v>3210.394</v>
+        <v>3211.08</v>
       </c>
       <c r="E14">
-        <v>4502.682</v>
+        <v>4498.342</v>
       </c>
       <c r="F14">
-        <v>6049.635</v>
+        <v>6051.531</v>
       </c>
       <c r="G14">
-        <v>5193.195</v>
+        <v>5198.421</v>
       </c>
       <c r="H14">
-        <v>6918.609</v>
+        <v>6918.895</v>
       </c>
       <c r="I14">
-        <v>64889262.466</v>
+        <v>64901152.258</v>
       </c>
       <c r="J14">
-        <v>54106121.602</v>
+        <v>54112165.184</v>
       </c>
       <c r="K14">
-        <v>75778043.185</v>
+        <v>75758738.65700001</v>
       </c>
       <c r="L14">
-        <v>804512988.38</v>
+        <v>804658942.795</v>
       </c>
       <c r="M14">
-        <v>690235596.021</v>
+        <v>690544005.446</v>
       </c>
       <c r="N14">
-        <v>919932971.476</v>
+        <v>919813911.261</v>
       </c>
     </row>
     <row r="15">
@@ -1062,40 +1062,40 @@
         </is>
       </c>
       <c r="C15">
-        <v>2869.454</v>
+        <v>2866.773</v>
       </c>
       <c r="D15">
-        <v>2331.619</v>
+        <v>2332.976</v>
       </c>
       <c r="E15">
-        <v>3417.958</v>
+        <v>3411.866</v>
       </c>
       <c r="F15">
-        <v>4475.637</v>
+        <v>4482.157</v>
       </c>
       <c r="G15">
-        <v>3823.8</v>
+        <v>3830.708</v>
       </c>
       <c r="H15">
-        <v>5136.455</v>
+        <v>5142.344</v>
       </c>
       <c r="I15">
-        <v>48284507.036</v>
+        <v>48245254.179</v>
       </c>
       <c r="J15">
-        <v>39210893.715</v>
+        <v>39212574.354</v>
       </c>
       <c r="K15">
-        <v>57482095.242</v>
+        <v>57412367.969</v>
       </c>
       <c r="L15">
-        <v>595153447.479</v>
+        <v>595974504.23</v>
       </c>
       <c r="M15">
-        <v>508667175.513</v>
+        <v>509549063.726</v>
       </c>
       <c r="N15">
-        <v>683721584.505</v>
+        <v>684057826.041</v>
       </c>
     </row>
     <row r="16">
@@ -1110,40 +1110,40 @@
         </is>
       </c>
       <c r="C16">
-        <v>6172.246</v>
+        <v>6171.073</v>
       </c>
       <c r="D16">
-        <v>5449.103</v>
+        <v>5447.974</v>
       </c>
       <c r="E16">
-        <v>6900.32</v>
+        <v>6898.374</v>
       </c>
       <c r="F16">
-        <v>10195.528</v>
+        <v>10200.839</v>
       </c>
       <c r="G16">
-        <v>9234.587</v>
+        <v>9238.254000000001</v>
       </c>
       <c r="H16">
-        <v>11171.817</v>
+        <v>11174.123</v>
       </c>
       <c r="I16">
-        <v>103950993.575</v>
+        <v>103937654.435</v>
       </c>
       <c r="J16">
-        <v>91745840.48899999</v>
+        <v>91779778.73899999</v>
       </c>
       <c r="K16">
-        <v>116253675.137</v>
+        <v>116222169.423</v>
       </c>
       <c r="L16">
-        <v>1356382880.416</v>
+        <v>1356855944.335</v>
       </c>
       <c r="M16">
-        <v>1227722751.682</v>
+        <v>1229022120.114</v>
       </c>
       <c r="N16">
-        <v>1485640570.627</v>
+        <v>1486062938.943</v>
       </c>
     </row>
     <row r="17">
@@ -1158,22 +1158,22 @@
         </is>
       </c>
       <c r="C17">
-        <v>28343.759</v>
+        <v>23586.362</v>
       </c>
       <c r="D17">
-        <v>25294.5</v>
+        <v>21034.938</v>
       </c>
       <c r="E17">
-        <v>31421.119</v>
+        <v>26194.549</v>
       </c>
       <c r="F17">
-        <v>72801.41800000001</v>
+        <v>6760.828</v>
       </c>
       <c r="G17">
-        <v>61131.643</v>
+        <v>5704.499</v>
       </c>
       <c r="H17">
-        <v>84934.40700000001</v>
+        <v>7882.738</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1185,13 +1185,13 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>9686107771.733999</v>
+        <v>899491491.699</v>
       </c>
       <c r="M17">
-        <v>8127525643.733</v>
+        <v>758481824.12</v>
       </c>
       <c r="N17">
-        <v>11291374319.692</v>
+        <v>1047852188.471</v>
       </c>
     </row>
     <row r="18">
@@ -1206,22 +1206,22 @@
         </is>
       </c>
       <c r="C18">
-        <v>22892.74</v>
+        <v>19047.043</v>
       </c>
       <c r="D18">
-        <v>20212.398</v>
+        <v>16793.968</v>
       </c>
       <c r="E18">
-        <v>25560.176</v>
+        <v>21303.433</v>
       </c>
       <c r="F18">
-        <v>60467.58</v>
+        <v>5620.893</v>
       </c>
       <c r="G18">
-        <v>51089.042</v>
+        <v>4754.333</v>
       </c>
       <c r="H18">
-        <v>69929.72500000001</v>
+        <v>6505.94</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1233,13 +1233,13 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>8044763724.531</v>
+        <v>747840174.668</v>
       </c>
       <c r="M18">
-        <v>6801072281.405</v>
+        <v>632880512.316</v>
       </c>
       <c r="N18">
-        <v>9302621375.25</v>
+        <v>865453342.99</v>
       </c>
     </row>
     <row r="19">
@@ -1254,22 +1254,22 @@
         </is>
       </c>
       <c r="C19">
-        <v>57440.682</v>
+        <v>47646.195</v>
       </c>
       <c r="D19">
-        <v>53567.512</v>
+        <v>44378.183</v>
       </c>
       <c r="E19">
-        <v>61319.314</v>
+        <v>50918.752</v>
       </c>
       <c r="F19">
-        <v>169282.145</v>
+        <v>15569.419</v>
       </c>
       <c r="G19">
-        <v>154518.189</v>
+        <v>14211.042</v>
       </c>
       <c r="H19">
-        <v>184136.713</v>
+        <v>16951.452</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1281,13 +1281,13 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>22515750666.343</v>
+        <v>2070901994.934</v>
       </c>
       <c r="M19">
-        <v>20569351515.57</v>
+        <v>1892036800.572</v>
       </c>
       <c r="N19">
-        <v>24493460101.304</v>
+        <v>2253975023.792</v>
       </c>
     </row>
     <row r="20">
@@ -1297,40 +1297,40 @@
         </is>
       </c>
       <c r="C20">
-        <v>185031.336</v>
+        <v>166676.938</v>
       </c>
       <c r="D20">
-        <v>166645.63</v>
+        <v>149823.875</v>
       </c>
       <c r="E20">
-        <v>203596.765</v>
+        <v>183755.505</v>
       </c>
       <c r="F20">
-        <v>394832.684</v>
+        <v>120331.378</v>
       </c>
       <c r="G20">
-        <v>348679.615</v>
+        <v>106695.973</v>
       </c>
       <c r="H20">
-        <v>441905.756</v>
+        <v>134382.11</v>
       </c>
       <c r="I20">
-        <v>2907836972.027</v>
+        <v>2910276331.815</v>
       </c>
       <c r="J20">
-        <v>2577185584.83</v>
+        <v>2578747606.99</v>
       </c>
       <c r="K20">
-        <v>3243562356.922</v>
+        <v>3246102177.214</v>
       </c>
       <c r="L20">
-        <v>52519779952.27299</v>
+        <v>16004155600.02</v>
       </c>
       <c r="M20">
-        <v>46395985789.06</v>
+        <v>14191970560.417</v>
       </c>
       <c r="N20">
-        <v>58774055186.654</v>
+        <v>17870056046.378</v>
       </c>
     </row>
     <row r="21">
@@ -1340,40 +1340,40 @@
         </is>
       </c>
       <c r="C21">
-        <v>246764.012</v>
+        <v>228406.308</v>
       </c>
       <c r="D21">
-        <v>220170.085</v>
+        <v>203340.002</v>
       </c>
       <c r="E21">
-        <v>273524.203</v>
+        <v>253672.622</v>
       </c>
       <c r="F21">
-        <v>977126.3110000001</v>
+        <v>702542.4110000002</v>
       </c>
       <c r="G21">
-        <v>882461.6869999999</v>
+        <v>640468.9859999998</v>
       </c>
       <c r="H21">
-        <v>1072742.647</v>
+        <v>765131.3110000002</v>
       </c>
       <c r="I21">
-        <v>2907836972.027</v>
+        <v>2910276331.815</v>
       </c>
       <c r="J21">
-        <v>2577185584.83</v>
+        <v>2578747606.99</v>
       </c>
       <c r="K21">
-        <v>3243562356.922</v>
+        <v>3246102177.214</v>
       </c>
       <c r="L21">
-        <v>129973972520.847</v>
+        <v>93448572425.62903</v>
       </c>
       <c r="M21">
-        <v>117373723834.58</v>
+        <v>85162955396.049</v>
       </c>
       <c r="N21">
-        <v>142716521228.174</v>
+        <v>101803822103.603</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Best practice/HIA_area_2019_1000replicate.xlsx
+++ b/output/Tables/Best practice/HIA_area_2019_1000replicate.xlsx
@@ -1,21 +1,120 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Best practice/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC2C423-4858-344E-93A7-CB4E992848CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="37440" yWindow="-1440" windowWidth="25960" windowHeight="16780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
+  <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>area_type</t>
+  </si>
+  <si>
+    <t>tot_cases</t>
+  </si>
+  <si>
+    <t>tot_cases_low</t>
+  </si>
+  <si>
+    <t>tot_cases_up</t>
+  </si>
+  <si>
+    <t>tot_daly</t>
+  </si>
+  <si>
+    <t>tot_daly_low</t>
+  </si>
+  <si>
+    <t>tot_daly_up</t>
+  </si>
+  <si>
+    <t>tot_medic_costs</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_low</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_up</t>
+  </si>
+  <si>
+    <t>tot_soc_costs</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_low</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_up</t>
+  </si>
+  <si>
+    <t>mort</t>
+  </si>
+  <si>
+    <t>periurban</t>
+  </si>
+  <si>
+    <t>rural</t>
+  </si>
+  <si>
+    <t>urban</t>
+  </si>
+  <si>
+    <t>cvd</t>
+  </si>
+  <si>
+    <t>cancer</t>
+  </si>
+  <si>
+    <t>diab2</t>
+  </si>
+  <si>
+    <t>dem</t>
+  </si>
+  <si>
+    <t>dep</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>Morbidity</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +162,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +214,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +248,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +283,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,104 +459,72 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>area_type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_low</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_up</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_low</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_up</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_low</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_up</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_low</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_up</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
       </c>
       <c r="C2">
-        <v>17297.015</v>
+        <v>17297.014999999999</v>
       </c>
       <c r="D2">
         <v>15546.688</v>
       </c>
       <c r="E2">
-        <v>19051.461</v>
+        <v>19051.460999999999</v>
       </c>
       <c r="F2">
-        <v>156123.485</v>
+        <v>156123.48499999999</v>
       </c>
       <c r="G2">
         <v>145839.976</v>
@@ -465,43 +542,39 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>20765612100.156</v>
+        <v>20765612100.155998</v>
       </c>
       <c r="M2">
-        <v>19391149302.275</v>
+        <v>19391149302.275002</v>
       </c>
       <c r="N2">
-        <v>22139529088.148</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>22139529088.147999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
       </c>
       <c r="C3">
-        <v>14421.137</v>
+        <v>14421.137000000001</v>
       </c>
       <c r="D3">
-        <v>13027.762</v>
+        <v>13027.762000000001</v>
       </c>
       <c r="E3">
         <v>15809.741</v>
       </c>
       <c r="F3">
-        <v>150023.904</v>
+        <v>150023.90400000001</v>
       </c>
       <c r="G3">
-        <v>140191.306</v>
+        <v>140191.30600000001</v>
       </c>
       <c r="H3">
-        <v>159888.716</v>
+        <v>159888.71599999999</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,25 +586,21 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>19950665546.293</v>
+        <v>19950665546.292999</v>
       </c>
       <c r="M3">
-        <v>18638561066.204</v>
+        <v>18638561066.203999</v>
       </c>
       <c r="N3">
-        <v>21275044775.269</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>21275044775.269001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
       </c>
       <c r="C4">
         <v>26774.77</v>
@@ -540,16 +609,16 @@
         <v>24775.445</v>
       </c>
       <c r="E4">
-        <v>28763.489</v>
+        <v>28763.489000000001</v>
       </c>
       <c r="F4">
-        <v>298583.004</v>
+        <v>298583.00400000002</v>
       </c>
       <c r="G4">
-        <v>284898.496</v>
+        <v>284898.49599999998</v>
       </c>
       <c r="H4">
-        <v>312266.269</v>
+        <v>312266.26899999997</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -561,100 +630,92 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>39717138240.38</v>
+        <v>39717138240.379997</v>
       </c>
       <c r="M4">
-        <v>37892182879.655</v>
+        <v>37892182879.654999</v>
       </c>
       <c r="N4">
-        <v>41553182267.878</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>41553182267.877998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>11472.925</v>
+        <v>11472.924999999999</v>
       </c>
       <c r="D5">
-        <v>10435.808</v>
+        <v>10435.808000000001</v>
       </c>
       <c r="E5">
-        <v>12524.763</v>
+        <v>12524.763000000001</v>
       </c>
       <c r="F5">
-        <v>9321.355</v>
+        <v>9321.3549999999996</v>
       </c>
       <c r="G5">
         <v>8541.73</v>
       </c>
       <c r="H5">
-        <v>10112.54</v>
+        <v>10112.540000000001</v>
       </c>
       <c r="I5">
-        <v>639083997.099</v>
+        <v>639083997.09899998</v>
       </c>
       <c r="J5">
-        <v>581084801.827</v>
+        <v>581084801.82700002</v>
       </c>
       <c r="K5">
-        <v>697712548.822</v>
+        <v>697712548.82200003</v>
       </c>
       <c r="L5">
-        <v>1239723582.979</v>
+        <v>1239723582.9790001</v>
       </c>
       <c r="M5">
-        <v>1135789542.261</v>
+        <v>1135789542.2609999</v>
       </c>
       <c r="N5">
-        <v>1345159125.143</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>1345159125.1429999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
       </c>
       <c r="C6">
-        <v>9713.377</v>
+        <v>9713.3770000000004</v>
       </c>
       <c r="D6">
-        <v>8827.186</v>
+        <v>8827.1859999999997</v>
       </c>
       <c r="E6">
         <v>10613.922</v>
       </c>
       <c r="F6">
-        <v>8712.075999999999</v>
+        <v>8712.0759999999991</v>
       </c>
       <c r="G6">
         <v>7948.56</v>
       </c>
       <c r="H6">
-        <v>9497.772000000001</v>
+        <v>9497.7720000000008</v>
       </c>
       <c r="I6">
-        <v>541206377.4170001</v>
+        <v>541206377.41700006</v>
       </c>
       <c r="J6">
-        <v>491723496.443</v>
+        <v>491723496.44300002</v>
       </c>
       <c r="K6">
-        <v>591471577.337</v>
+        <v>591471577.33700001</v>
       </c>
       <c r="L6">
         <v>1159009885.987</v>
@@ -666,16 +727,12 @@
         <v>1263354825.243</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
       </c>
       <c r="C7">
         <v>18947.677</v>
@@ -684,13 +741,13 @@
         <v>17723.088</v>
       </c>
       <c r="E7">
-        <v>20182.937</v>
+        <v>20182.937000000002</v>
       </c>
       <c r="F7">
-        <v>17888.351</v>
+        <v>17888.350999999999</v>
       </c>
       <c r="G7">
-        <v>16861.307</v>
+        <v>16861.307000000001</v>
       </c>
       <c r="H7">
         <v>18927.608</v>
@@ -699,55 +756,51 @@
         <v>1055517058.74</v>
       </c>
       <c r="J7">
-        <v>987045327.9400001</v>
+        <v>987045327.94000006</v>
       </c>
       <c r="K7">
-        <v>1124508490.134</v>
+        <v>1124508490.1340001</v>
       </c>
       <c r="L7">
-        <v>2379377282.076</v>
+        <v>2379377282.0760002</v>
       </c>
       <c r="M7">
-        <v>2242452418.479</v>
+        <v>2242452418.4790001</v>
       </c>
       <c r="N7">
-        <v>2517129625.951</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>2517129625.9510002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>8092.691</v>
+        <v>8092.6909999999998</v>
       </c>
       <c r="D8">
-        <v>7286.138</v>
+        <v>7286.1379999999999</v>
       </c>
       <c r="E8">
-        <v>8935.870999999999</v>
+        <v>8935.8709999999992</v>
       </c>
       <c r="F8">
-        <v>11163.711</v>
+        <v>11163.710999999999</v>
       </c>
       <c r="G8">
-        <v>9772.101000000001</v>
+        <v>9772.1010000000006</v>
       </c>
       <c r="H8">
-        <v>12720.468</v>
+        <v>12720.468000000001</v>
       </c>
       <c r="I8">
         <v>119799970.005</v>
       </c>
       <c r="J8">
-        <v>107881367.136</v>
+        <v>107881367.13600001</v>
       </c>
       <c r="K8">
         <v>132329000.068</v>
@@ -762,19 +815,15 @@
         <v>1691703090.908</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
       </c>
       <c r="C9">
-        <v>6844.618</v>
+        <v>6844.6180000000004</v>
       </c>
       <c r="D9">
         <v>6181.848</v>
@@ -786,16 +835,16 @@
         <v>9568.643</v>
       </c>
       <c r="G9">
-        <v>8494.361000000001</v>
+        <v>8494.3610000000008</v>
       </c>
       <c r="H9">
         <v>10734.445</v>
       </c>
       <c r="I9">
-        <v>101309575.762</v>
+        <v>101309575.76199999</v>
       </c>
       <c r="J9">
-        <v>91513640.325</v>
+        <v>91513640.325000003</v>
       </c>
       <c r="K9">
         <v>111672984.301</v>
@@ -804,88 +853,80 @@
         <v>1272156968.585</v>
       </c>
       <c r="M9">
-        <v>1130083001.31</v>
+        <v>1130083001.3099999</v>
       </c>
       <c r="N9">
         <v>1427687095.546</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
       </c>
       <c r="C10">
         <v>16267.713</v>
       </c>
       <c r="D10">
-        <v>15186.183</v>
+        <v>15186.183000000001</v>
       </c>
       <c r="E10">
         <v>17394.517</v>
       </c>
       <c r="F10">
-        <v>26280.255</v>
+        <v>26280.255000000001</v>
       </c>
       <c r="G10">
         <v>24223.909</v>
       </c>
       <c r="H10">
-        <v>28451.792</v>
+        <v>28451.792000000001</v>
       </c>
       <c r="I10">
-        <v>240891229.837</v>
+        <v>240891229.83700001</v>
       </c>
       <c r="J10">
-        <v>224859849.878</v>
+        <v>224859849.87799999</v>
       </c>
       <c r="K10">
-        <v>257653995.721</v>
+        <v>257653995.72099999</v>
       </c>
       <c r="L10">
-        <v>3494967615.946</v>
+        <v>3494967615.9460001</v>
       </c>
       <c r="M10">
-        <v>3222948265.595</v>
+        <v>3222948265.5949998</v>
       </c>
       <c r="N10">
-        <v>3783553944.516</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>3783553944.5159998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
       </c>
       <c r="C11">
         <v>1600.047</v>
       </c>
       <c r="D11">
-        <v>1437.474</v>
+        <v>1437.4739999999999</v>
       </c>
       <c r="E11">
         <v>1770.453</v>
       </c>
       <c r="F11">
-        <v>2861.881</v>
+        <v>2861.8809999999999</v>
       </c>
       <c r="G11">
-        <v>2563.253</v>
+        <v>2563.2530000000002</v>
       </c>
       <c r="H11">
-        <v>3174.396</v>
+        <v>3174.3960000000002</v>
       </c>
       <c r="I11">
         <v>120341117.529</v>
@@ -897,28 +938,24 @@
         <v>133122961.199</v>
       </c>
       <c r="L11">
-        <v>380643427.115</v>
+        <v>380643427.11500001</v>
       </c>
       <c r="M11">
-        <v>340935925.642</v>
+        <v>340935925.64200002</v>
       </c>
       <c r="N11">
-        <v>422261729.862</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>422261729.86199999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
       </c>
       <c r="C12">
-        <v>1440.782</v>
+        <v>1440.7819999999999</v>
       </c>
       <c r="D12">
         <v>1293.136</v>
@@ -927,148 +964,136 @@
         <v>1594.855</v>
       </c>
       <c r="F12">
-        <v>2647.575</v>
+        <v>2647.5749999999998</v>
       </c>
       <c r="G12">
-        <v>2369.506</v>
+        <v>2369.5059999999999</v>
       </c>
       <c r="H12">
         <v>2939.902</v>
       </c>
       <c r="I12">
-        <v>108370155.887</v>
+        <v>108370155.88699999</v>
       </c>
       <c r="J12">
-        <v>97336795.15099999</v>
+        <v>97336795.150999993</v>
       </c>
       <c r="K12">
         <v>119918234.013</v>
       </c>
       <c r="L12">
-        <v>352030795.456</v>
+        <v>352030795.45599997</v>
       </c>
       <c r="M12">
-        <v>315312476.419</v>
+        <v>315312476.41900003</v>
       </c>
       <c r="N12">
-        <v>390860248.244</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>390860248.24400002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
       </c>
       <c r="C13">
-        <v>3361.316</v>
+        <v>3361.3159999999998</v>
       </c>
       <c r="D13">
-        <v>3132.525</v>
+        <v>3132.5250000000001</v>
       </c>
       <c r="E13">
         <v>3596.252</v>
       </c>
       <c r="F13">
-        <v>6991.624</v>
+        <v>6991.6239999999998</v>
       </c>
       <c r="G13">
         <v>6501.268</v>
       </c>
       <c r="H13">
-        <v>7501.719</v>
+        <v>7501.7190000000001</v>
       </c>
       <c r="I13">
-        <v>252797211.378</v>
+        <v>252797211.37799999</v>
       </c>
       <c r="J13">
         <v>235549603.588</v>
       </c>
       <c r="K13">
-        <v>270469842.189</v>
+        <v>270469842.18900001</v>
       </c>
       <c r="L13">
-        <v>929753252.064</v>
+        <v>929753252.06400001</v>
       </c>
       <c r="M13">
         <v>864354678.102</v>
       </c>
       <c r="N13">
-        <v>997489931.5650001</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>997489931.56500006</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
       </c>
       <c r="C14">
-        <v>4169.365</v>
+        <v>4169.3649999999998</v>
       </c>
       <c r="D14">
         <v>3685.52</v>
       </c>
       <c r="E14">
-        <v>4658.943</v>
+        <v>4658.9430000000002</v>
       </c>
       <c r="F14">
-        <v>6387.084</v>
+        <v>6387.0839999999998</v>
       </c>
       <c r="G14">
-        <v>5724.156</v>
+        <v>5724.1559999999999</v>
       </c>
       <c r="H14">
-        <v>7064.649</v>
+        <v>7064.6490000000003</v>
       </c>
       <c r="I14">
-        <v>70211776.04899999</v>
+        <v>70211776.048999995</v>
       </c>
       <c r="J14">
-        <v>62094856.609</v>
+        <v>62094856.608999997</v>
       </c>
       <c r="K14">
-        <v>78461542.69</v>
+        <v>78461542.689999998</v>
       </c>
       <c r="L14">
-        <v>849464958.663</v>
+        <v>849464958.66299999</v>
       </c>
       <c r="M14">
-        <v>760911541.575</v>
+        <v>760911541.57500005</v>
       </c>
       <c r="N14">
-        <v>939517362.214</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>939517362.21399999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
       </c>
       <c r="C15">
-        <v>3218.314</v>
+        <v>3218.3139999999999</v>
       </c>
       <c r="D15">
-        <v>2811.836</v>
+        <v>2811.8359999999998</v>
       </c>
       <c r="E15">
-        <v>3636.602</v>
+        <v>3636.6019999999999</v>
       </c>
       <c r="F15">
         <v>5523.85</v>
@@ -1077,49 +1102,45 @@
         <v>4988.174</v>
       </c>
       <c r="H15">
-        <v>6070.321</v>
+        <v>6070.3209999999999</v>
       </c>
       <c r="I15">
         <v>54189470.423</v>
       </c>
       <c r="J15">
-        <v>47326661.361</v>
+        <v>47326661.361000001</v>
       </c>
       <c r="K15">
-        <v>61180520.443</v>
+        <v>61180520.443000004</v>
       </c>
       <c r="L15">
-        <v>734545449.577</v>
+        <v>734545449.57700002</v>
       </c>
       <c r="M15">
-        <v>663765127.553</v>
+        <v>663765127.55299997</v>
       </c>
       <c r="N15">
-        <v>807677453.1160001</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>807677453.11600006</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
       </c>
       <c r="C16">
         <v>6543.415</v>
       </c>
       <c r="D16">
-        <v>5954.712</v>
+        <v>5954.7120000000004</v>
       </c>
       <c r="E16">
-        <v>7137.352</v>
+        <v>7137.3519999999999</v>
       </c>
       <c r="F16">
-        <v>11338.719</v>
+        <v>11338.718999999999</v>
       </c>
       <c r="G16">
         <v>10506.971</v>
@@ -1128,7 +1149,7 @@
         <v>12184.02</v>
       </c>
       <c r="I16">
-        <v>110187262.65</v>
+        <v>110187262.65000001</v>
       </c>
       <c r="J16">
         <v>100273396.118</v>
@@ -1146,16 +1167,12 @@
         <v>1620408894.188</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
       </c>
       <c r="C17">
         <v>30571.895</v>
@@ -1164,16 +1181,16 @@
         <v>27935.269</v>
       </c>
       <c r="E17">
-        <v>33304.491</v>
+        <v>33304.491000000002</v>
       </c>
       <c r="F17">
-        <v>9158.359</v>
+        <v>9158.3590000000004</v>
       </c>
       <c r="G17">
-        <v>8027.202</v>
+        <v>8027.2020000000002</v>
       </c>
       <c r="H17">
-        <v>10405.255</v>
+        <v>10405.254999999999</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1185,37 +1202,33 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>1218117987.226</v>
+        <v>1218117987.2260001</v>
       </c>
       <c r="M17">
         <v>1067625703.747</v>
       </c>
       <c r="N17">
-        <v>1384341413.386</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>1384341413.3859999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
       </c>
       <c r="C18">
         <v>25994.304</v>
       </c>
       <c r="D18">
-        <v>23952.951</v>
+        <v>23952.951000000001</v>
       </c>
       <c r="E18">
-        <v>28050.902</v>
+        <v>28050.901999999998</v>
       </c>
       <c r="F18">
-        <v>7831.588</v>
+        <v>7831.5879999999997</v>
       </c>
       <c r="G18">
         <v>7050.549</v>
@@ -1236,40 +1249,36 @@
         <v>1041886858.591</v>
       </c>
       <c r="M18">
-        <v>937609018.223</v>
+        <v>937609018.22300005</v>
       </c>
       <c r="N18">
-        <v>1149686715.113</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>1149686715.1129999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
       </c>
       <c r="C19">
-        <v>69380.766</v>
+        <v>69380.766000000003</v>
       </c>
       <c r="D19">
-        <v>65632.546</v>
+        <v>65632.546000000002</v>
       </c>
       <c r="E19">
-        <v>73170.717</v>
+        <v>73170.717000000004</v>
       </c>
       <c r="F19">
-        <v>23998.068</v>
+        <v>23998.067999999999</v>
       </c>
       <c r="G19">
-        <v>22319.579</v>
+        <v>22319.579000000002</v>
       </c>
       <c r="H19">
-        <v>25720.649</v>
+        <v>25720.649000000001</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1281,91 +1290,83 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>3192408477.905</v>
+        <v>3192408477.9050002</v>
       </c>
       <c r="M19">
-        <v>2969204899.574</v>
+        <v>2969204899.5739999</v>
       </c>
       <c r="N19">
         <v>3421886115.882</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
       </c>
       <c r="C20">
-        <v>31205.022</v>
+        <v>31205.022000000001</v>
       </c>
       <c r="D20">
-        <v>28654.169</v>
+        <v>28654.169000000002</v>
       </c>
       <c r="E20">
-        <v>33869.93799999999</v>
+        <v>33869.937999999987</v>
       </c>
       <c r="F20">
-        <v>47012.609</v>
+        <v>47012.608999999997</v>
       </c>
       <c r="G20">
-        <v>42490.371</v>
+        <v>42490.370999999999</v>
       </c>
       <c r="H20">
-        <v>51906.705</v>
+        <v>51906.705000000002</v>
       </c>
       <c r="I20">
-        <v>462000775.604</v>
+        <v>462000775.60399997</v>
       </c>
       <c r="J20">
-        <v>424254857.339</v>
+        <v>424254857.33899999</v>
       </c>
       <c r="K20">
-        <v>501655980.09</v>
+        <v>501655980.08999997</v>
       </c>
       <c r="L20">
-        <v>6251696444.469</v>
+        <v>6251696444.4689999</v>
       </c>
       <c r="M20">
-        <v>5652135967.628</v>
+        <v>5652135967.6280003</v>
       </c>
       <c r="N20">
-        <v>6902944130.969999</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>6902944130.9699993</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
       </c>
       <c r="C21">
-        <v>40133.979</v>
+        <v>40133.978999999999</v>
       </c>
       <c r="D21">
-        <v>36986.08199999999</v>
+        <v>36986.081999999988</v>
       </c>
       <c r="E21">
-        <v>43321.622</v>
+        <v>43321.622000000003</v>
       </c>
       <c r="F21">
-        <v>35921.78199999999</v>
+        <v>35921.781999999992</v>
       </c>
       <c r="G21">
-        <v>33351.597</v>
+        <v>33351.597000000002</v>
       </c>
       <c r="H21">
-        <v>38537.92</v>
+        <v>38537.919999999998</v>
       </c>
       <c r="I21">
         <v>2235807433.256</v>
@@ -1374,49 +1375,45 @@
         <v>2059853626.21</v>
       </c>
       <c r="K21">
-        <v>2413692616.293</v>
+        <v>2413692616.2930002</v>
       </c>
       <c r="L21">
-        <v>4778110751.042</v>
+        <v>4778110751.0419998</v>
       </c>
       <c r="M21">
-        <v>4435748156.298</v>
+        <v>4435748156.2980003</v>
       </c>
       <c r="N21">
-        <v>5125643576.337</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>5125643576.3369999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>23</v>
       </c>
       <c r="C22">
-        <v>13931.094</v>
+        <v>13931.093999999999</v>
       </c>
       <c r="D22">
-        <v>12452.068</v>
+        <v>12452.067999999999</v>
       </c>
       <c r="E22">
-        <v>15432.897</v>
+        <v>15432.897000000001</v>
       </c>
       <c r="F22">
-        <v>23249.653</v>
+        <v>23249.652999999998</v>
       </c>
       <c r="G22">
-        <v>21219.301</v>
+        <v>21219.300999999999</v>
       </c>
       <c r="H22">
         <v>25318.99</v>
       </c>
       <c r="I22">
-        <v>234588509.122</v>
+        <v>234588509.12200001</v>
       </c>
       <c r="J22">
         <v>209694914.088</v>
@@ -1428,22 +1425,18 @@
         <v>3092463141.915</v>
       </c>
       <c r="M22">
-        <v>2822112635.94</v>
+        <v>2822112635.9400001</v>
       </c>
       <c r="N22">
-        <v>3367603709.518</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>3367603709.5180001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>23</v>
       </c>
       <c r="C23">
         <v>125946.965</v>
@@ -1452,16 +1445,16 @@
         <v>117520.766</v>
       </c>
       <c r="E23">
-        <v>134526.11</v>
+        <v>134526.10999999999</v>
       </c>
       <c r="F23">
-        <v>40988.015</v>
+        <v>40988.014999999999</v>
       </c>
       <c r="G23">
         <v>37397.33</v>
       </c>
       <c r="H23">
-        <v>44765.63400000001</v>
+        <v>44765.634000000013</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1473,34 +1466,30 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>5452413323.722</v>
+        <v>5452413323.7220001</v>
       </c>
       <c r="M23">
-        <v>4974439621.544</v>
+        <v>4974439621.5439997</v>
       </c>
       <c r="N23">
-        <v>5955914244.381</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>5955914244.3809996</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" t="s">
+        <v>23</v>
       </c>
       <c r="C24">
-        <v>6402.145</v>
+        <v>6402.1450000000004</v>
       </c>
       <c r="D24">
-        <v>5863.135</v>
+        <v>5863.1350000000002</v>
       </c>
       <c r="E24">
-        <v>6961.559999999999</v>
+        <v>6961.5599999999986</v>
       </c>
       <c r="F24">
         <v>12501.08</v>
@@ -1512,52 +1501,48 @@
         <v>13616.017</v>
       </c>
       <c r="I24">
-        <v>481508484.794</v>
+        <v>481508484.79400003</v>
       </c>
       <c r="J24">
-        <v>440919731.158</v>
+        <v>440919731.15799999</v>
       </c>
       <c r="K24">
-        <v>523511037.401</v>
+        <v>523511037.40100002</v>
       </c>
       <c r="L24">
         <v>1662427474.635</v>
       </c>
       <c r="M24">
-        <v>1520603080.163</v>
+        <v>1520603080.1630001</v>
       </c>
       <c r="N24">
         <v>1810611909.671</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>23</v>
       </c>
       <c r="C25">
-        <v>58492.92200000001</v>
+        <v>58492.922000000013</v>
       </c>
       <c r="D25">
-        <v>53349.895</v>
+        <v>53349.894999999997</v>
       </c>
       <c r="E25">
-        <v>63624.691</v>
+        <v>63624.690999999999</v>
       </c>
       <c r="F25">
-        <v>604730.3929999999</v>
+        <v>604730.39299999992</v>
       </c>
       <c r="G25">
-        <v>570929.7779999999</v>
+        <v>570929.77799999993</v>
       </c>
       <c r="H25">
-        <v>638623.963</v>
+        <v>638623.96299999999</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1569,49 +1554,45 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>80433415886.82899</v>
+        <v>80433415886.828995</v>
       </c>
       <c r="M25">
-        <v>75921893248.134</v>
+        <v>75921893248.134003</v>
       </c>
       <c r="N25">
-        <v>84967756131.295</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>84967756131.294998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>15</v>
       </c>
       <c r="C26">
-        <v>73203.93799999999</v>
+        <v>73203.937999999995</v>
       </c>
       <c r="D26">
-        <v>66326.897</v>
+        <v>66326.896999999997</v>
       </c>
       <c r="E26">
-        <v>80245.982</v>
+        <v>80245.982000000004</v>
       </c>
       <c r="F26">
         <v>195015.875</v>
       </c>
       <c r="G26">
-        <v>180468.418</v>
+        <v>180468.41800000001</v>
       </c>
       <c r="H26">
-        <v>209946.286</v>
+        <v>209946.28599999999</v>
       </c>
       <c r="I26">
-        <v>949436860.682</v>
+        <v>949436860.68200004</v>
       </c>
       <c r="J26">
-        <v>859094357.9910001</v>
+        <v>859094357.99100006</v>
       </c>
       <c r="K26">
         <v>1041626052.779</v>
@@ -1623,25 +1604,21 @@
         <v>23995516716.223</v>
       </c>
       <c r="N26">
-        <v>27922511809.661</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>27922511809.660999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
       </c>
       <c r="C27">
-        <v>61632.53200000001</v>
+        <v>61632.532000000007</v>
       </c>
       <c r="D27">
-        <v>56094.719</v>
+        <v>56094.718999999997</v>
       </c>
       <c r="E27">
         <v>67245.572</v>
@@ -1650,151 +1627,139 @@
         <v>184307.636</v>
       </c>
       <c r="G27">
-        <v>171042.456</v>
+        <v>171042.45600000001</v>
       </c>
       <c r="H27">
         <v>197770.886</v>
       </c>
       <c r="I27">
-        <v>805075579.489</v>
+        <v>805075579.48899996</v>
       </c>
       <c r="J27">
-        <v>727900593.28</v>
+        <v>727900593.27999997</v>
       </c>
       <c r="K27">
-        <v>884243316.094</v>
+        <v>884243316.09399998</v>
       </c>
       <c r="L27">
-        <v>24510295504.489</v>
+        <v>24510295504.488998</v>
       </c>
       <c r="M27">
-        <v>22742836885.267</v>
+        <v>22742836885.266998</v>
       </c>
       <c r="N27">
-        <v>26314311112.531</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>26314311112.530998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" t="s">
+        <v>17</v>
       </c>
       <c r="C28">
-        <v>141275.657</v>
+        <v>141275.65700000001</v>
       </c>
       <c r="D28">
-        <v>132404.499</v>
+        <v>132404.49900000001</v>
       </c>
       <c r="E28">
         <v>150245.264</v>
       </c>
       <c r="F28">
-        <v>385080.0210000001</v>
+        <v>385080.02100000012</v>
       </c>
       <c r="G28">
         <v>365311.53</v>
       </c>
       <c r="H28">
-        <v>405052.057</v>
+        <v>405052.05699999997</v>
       </c>
       <c r="I28">
         <v>1659392762.605</v>
       </c>
       <c r="J28">
-        <v>1547728177.524</v>
+        <v>1547728177.5239999</v>
       </c>
       <c r="K28">
-        <v>1772892791.742</v>
+        <v>1772892791.7420001</v>
       </c>
       <c r="L28">
-        <v>51222097602.046</v>
+        <v>51222097602.045998</v>
       </c>
       <c r="M28">
-        <v>48588579108.217</v>
+        <v>48588579108.217003</v>
       </c>
       <c r="N28">
-        <v>53893650779.98</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>53893650779.980003</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" t="s">
+        <v>23</v>
       </c>
       <c r="C29">
-        <v>276112.127</v>
+        <v>276112.12699999998</v>
       </c>
       <c r="D29">
-        <v>254826.115</v>
+        <v>254826.11499999999</v>
       </c>
       <c r="E29">
-        <v>297736.8180000001</v>
+        <v>297736.81800000009</v>
       </c>
       <c r="F29">
-        <v>764403.532</v>
+        <v>764403.53200000001</v>
       </c>
       <c r="G29">
-        <v>716822.4040000002</v>
+        <v>716822.40400000021</v>
       </c>
       <c r="H29">
-        <v>812769.2289999999</v>
+        <v>812769.22899999993</v>
       </c>
       <c r="I29">
         <v>3413905202.776</v>
       </c>
       <c r="J29">
-        <v>3134723128.795</v>
+        <v>3134723128.7950001</v>
       </c>
       <c r="K29">
-        <v>3698762160.615</v>
+        <v>3698762160.6149998</v>
       </c>
       <c r="L29">
         <v>101670527022.612</v>
       </c>
       <c r="M29">
-        <v>95326932709.70702</v>
+        <v>95326932709.707016</v>
       </c>
       <c r="N29">
         <v>108130473702.172</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Morbidity</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" t="s">
+        <v>23</v>
       </c>
       <c r="C30">
-        <v>217619.205</v>
+        <v>217619.20499999999</v>
       </c>
       <c r="D30">
         <v>201476.22</v>
       </c>
       <c r="E30">
-        <v>234112.127</v>
+        <v>234112.12700000001</v>
       </c>
       <c r="F30">
         <v>159673.139</v>
       </c>
       <c r="G30">
-        <v>145892.626</v>
+        <v>145892.62599999999</v>
       </c>
       <c r="H30">
         <v>174145.266</v>
@@ -1803,19 +1768,19 @@
         <v>3413905202.776</v>
       </c>
       <c r="J30">
-        <v>3134723128.795</v>
+        <v>3134723128.7950001</v>
       </c>
       <c r="K30">
-        <v>3698762160.615</v>
+        <v>3698762160.6149998</v>
       </c>
       <c r="L30">
-        <v>21237111135.783</v>
+        <v>21237111135.783001</v>
       </c>
       <c r="M30">
-        <v>19405039461.573</v>
+        <v>19405039461.573002</v>
       </c>
       <c r="N30">
-        <v>23162717570.877</v>
+        <v>23162717570.876999</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Best practice/HIA_area_2019_1000replicate.xlsx
+++ b/output/Tables/Best practice/HIA_area_2019_1000replicate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Best practice/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC2C423-4858-344E-93A7-CB4E992848CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F1297D-9BA4-BD4C-BFA5-7A15FCE4EDAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="37440" yWindow="-1440" windowWidth="25960" windowHeight="16780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
